--- a/麻坛所有比赛数据.xlsx
+++ b/麻坛所有比赛数据.xlsx
@@ -1,36 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2420" yWindow="5670" windowWidth="18470" windowHeight="15460" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="比赛汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="对局明细_20260620" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="对局明细_20260621" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="比赛汇总" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="对局明细_20260621" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="对局明细_20260620" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -58,7 +52,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -421,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -649,6 +643,50 @@
         </is>
       </c>
       <c r="J5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>比赛_20260621</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -663,7 +701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -709,7 +747,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>阿狗(东风)</t>
+          <t>奶猫(东风)</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -734,7 +772,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -752,7 +790,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -782,7 +820,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -795,33 +833,33 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>放炮</t>
+          <t>自摸</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>/</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
-        <v>-4</v>
+        <v>120</v>
       </c>
       <c r="J3" t="n">
-        <v>-1</v>
+        <v>-40</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>-40</v>
       </c>
       <c r="L3" t="n">
-        <v>-1</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="4">
@@ -830,46 +868,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>第一庄（2倍）</t>
+          <t>第二庄（4倍）</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>放炮</t>
+          <t>自摸</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>/</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>-4</v>
+        <v>240</v>
       </c>
       <c r="J4" t="n">
-        <v>-1</v>
+        <v>-80</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>-80</v>
       </c>
       <c r="L4" t="n">
-        <v>-1</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="5">
@@ -878,334 +916,46 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>第一庄（2倍）</t>
+          <t>第三庄及以上（8倍）</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>放炮</t>
+          <t>自摸</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>老野</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>/</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>-4</v>
+        <v>-160</v>
       </c>
       <c r="J5" t="n">
-        <v>-1</v>
+        <v>-20</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>-20</v>
       </c>
       <c r="L5" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>老王</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>老王</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>6</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>老王</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>6</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>老王</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>老王</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>6</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>老王</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>6</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-1</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -1219,7 +969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1303,33 +1053,33 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>放炮</t>
+          <t>自摸</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>阿狗</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>/</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J2" t="n">
         <v>-4</v>
       </c>
-      <c r="J2" t="n">
-        <v>-1</v>
-      </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
       <c r="L2" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="3">
@@ -1761,438 +1511,6 @@
         <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>农少</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>农少</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>6</v>
-      </c>
-      <c r="K13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>农少</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>6</v>
-      </c>
-      <c r="K14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>农少</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J15" t="n">
-        <v>6</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>农少</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J16" t="n">
-        <v>6</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>农少</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>6</v>
-      </c>
-      <c r="K17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>农少</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>6</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>农少</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J19" t="n">
-        <v>6</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>农少</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J20" t="n">
-        <v>6</v>
-      </c>
-      <c r="K20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L20" t="n">
         <v>-1</v>
       </c>
     </row>

--- a/麻坛所有比赛数据.xlsx
+++ b/麻坛所有比赛数据.xlsx
@@ -659,7 +659,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>老王</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -667,7 +667,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>老野</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -675,7 +675,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老野</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -683,7 +683,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -701,7 +701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,33 +785,33 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>自摸</t>
+          <t>放炮</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>奶猫</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
+        <v>-72</v>
       </c>
       <c r="J2" t="n">
-        <v>-4</v>
+        <v>-18</v>
       </c>
       <c r="K2" t="n">
-        <v>-4</v>
+        <v>108</v>
       </c>
       <c r="L2" t="n">
-        <v>-4</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="3">
@@ -833,33 +833,33 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>自摸</t>
+          <t>放炮</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>奶猫</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I3" t="n">
-        <v>120</v>
+        <v>-72</v>
       </c>
       <c r="J3" t="n">
-        <v>-40</v>
+        <v>-18</v>
       </c>
       <c r="K3" t="n">
-        <v>-40</v>
+        <v>108</v>
       </c>
       <c r="L3" t="n">
-        <v>-40</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="4">
@@ -873,41 +873,41 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>第二庄（4倍）</t>
+          <t>第一庄（2倍）</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>自摸</t>
+          <t>放炮</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>奶猫</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I4" t="n">
-        <v>240</v>
+        <v>-72</v>
       </c>
       <c r="J4" t="n">
-        <v>-80</v>
+        <v>-18</v>
       </c>
       <c r="K4" t="n">
-        <v>-80</v>
+        <v>108</v>
       </c>
       <c r="L4" t="n">
-        <v>-80</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="5">
@@ -921,41 +921,137 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>第三庄及以上（8倍）</t>
+          <t>第一庄（2倍）</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>18</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-72</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-18</v>
+      </c>
+      <c r="K5" t="n">
+        <v>108</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>自摸</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>老野</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>10</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-160</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-20</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-20</v>
-      </c>
-      <c r="L5" t="n">
-        <v>200</v>
+      <c r="H6" t="n">
+        <v>18</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-72</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-36</v>
+      </c>
+      <c r="K6" t="n">
+        <v>144</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-36</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>18</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-72</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-36</v>
+      </c>
+      <c r="K7" t="n">
+        <v>144</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-36</v>
       </c>
     </row>
   </sheetData>

--- a/麻坛所有比赛数据.xlsx
+++ b/麻坛所有比赛数据.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="比赛汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="对局明细_20260621" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="对局明细_20260622" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="对局明细_20260620" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="对局明细_20260621" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -654,12 +655,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -675,15 +676,15 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>老野</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>奶猫</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -701,7 +702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,33 +786,33 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>放炮</t>
+          <t>自摸</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>/</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>-72</v>
+        <v>12</v>
       </c>
       <c r="J2" t="n">
-        <v>-18</v>
+        <v>-4</v>
       </c>
       <c r="K2" t="n">
-        <v>108</v>
+        <v>-4</v>
       </c>
       <c r="L2" t="n">
-        <v>-18</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="3">
@@ -833,33 +834,33 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>放炮</t>
+          <t>自摸</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>/</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>-72</v>
+        <v>60</v>
       </c>
       <c r="J3" t="n">
-        <v>-18</v>
+        <v>-20</v>
       </c>
       <c r="K3" t="n">
-        <v>108</v>
+        <v>-20</v>
       </c>
       <c r="L3" t="n">
-        <v>-18</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="4">
@@ -881,33 +882,33 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>放炮</t>
+          <t>自摸</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>/</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>-72</v>
+        <v>60</v>
       </c>
       <c r="J4" t="n">
-        <v>-18</v>
+        <v>-20</v>
       </c>
       <c r="K4" t="n">
-        <v>108</v>
+        <v>-20</v>
       </c>
       <c r="L4" t="n">
-        <v>-18</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="5">
@@ -929,33 +930,33 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>放炮</t>
+          <t>自摸</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>/</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>-72</v>
+        <v>60</v>
       </c>
       <c r="J5" t="n">
-        <v>-18</v>
+        <v>-20</v>
       </c>
       <c r="K5" t="n">
-        <v>108</v>
+        <v>-20</v>
       </c>
       <c r="L5" t="n">
-        <v>-18</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="6">
@@ -982,7 +983,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -991,19 +992,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>-72</v>
+        <v>-20</v>
       </c>
       <c r="J6" t="n">
-        <v>-36</v>
+        <v>40</v>
       </c>
       <c r="K6" t="n">
-        <v>144</v>
+        <v>-10</v>
       </c>
       <c r="L6" t="n">
-        <v>-36</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="7">
@@ -1030,28 +1031,124 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J7" t="n">
+        <v>40</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>老王</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>/</t>
         </is>
       </c>
-      <c r="H7" t="n">
-        <v>18</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-72</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-36</v>
-      </c>
-      <c r="K7" t="n">
-        <v>144</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-36</v>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K8" t="n">
+        <v>40</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1613,4 +1710,992 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>局号</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>庄家</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>连庄次数</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>庄倍数</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>本局结果</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>胡牌选手</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>放炮选手</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>番数</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>阿狗(东风)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>农少(南风)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>老王(西风)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>老野(北风)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>6</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>6</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>6</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/麻坛所有比赛数据.xlsx
+++ b/麻坛所有比赛数据.xlsx
@@ -650,7 +650,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>比赛_20260621</t>
+          <t>比赛_20260622</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -702,7 +702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -848,19 +848,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
       <c r="K3" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
       <c r="L3" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="4">
@@ -896,19 +896,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
       <c r="K4" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
       <c r="L4" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="5">
@@ -944,19 +944,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
       <c r="K5" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
       <c r="L5" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="6">
@@ -983,7 +983,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -992,163 +992,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>-20</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>40</v>
+        <v>-4</v>
       </c>
       <c r="K6" t="n">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="L6" t="n">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>奶猫</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>自摸</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>农少</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>5</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J7" t="n">
-        <v>40</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-10</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>奶猫</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>自摸</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>老王</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-10</v>
-      </c>
-      <c r="K8" t="n">
-        <v>40</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>奶猫</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>老野</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>奶猫</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>5</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-5</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L9" t="n">
-        <v>30</v>
+        <v>-4</v>
       </c>
     </row>
   </sheetData>

--- a/麻坛所有比赛数据.xlsx
+++ b/麻坛所有比赛数据.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="比赛汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="对局明细_20260622" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="对局明细_20260620" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="对局明细_20260621" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="对局明细_20260623" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="对局明细_20260622" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="对局明细_20260620" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="对局明细_20260621" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -688,6 +689,50 @@
         </is>
       </c>
       <c r="J6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>比赛_20260623</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>老潘</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -702,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,17 +793,17 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>奶猫(东风)</t>
+          <t>农少(东风)</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>农少(南风)</t>
+          <t>老王(南风)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>老王(西风)</t>
+          <t>老潘(西风)</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
@@ -773,7 +818,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -791,7 +836,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -800,19 +845,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="J2" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
       <c r="K2" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
       <c r="L2" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="3">
@@ -821,7 +866,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -839,7 +884,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -848,19 +893,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="J3" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
       <c r="K3" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
       <c r="L3" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="4">
@@ -869,7 +914,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -887,7 +932,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -896,19 +941,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="J4" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
       <c r="K4" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
       <c r="L4" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="5">
@@ -917,7 +962,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -935,7 +980,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -944,19 +989,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="J5" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
       <c r="K5" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
       <c r="L5" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="6">
@@ -965,7 +1010,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -983,7 +1028,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -992,19 +1037,451 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I6" t="n">
+        <v>120</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-40</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-40</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" t="n">
+        <v>120</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-40</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-40</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" t="n">
+        <v>120</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-40</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-40</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" t="n">
+        <v>120</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-40</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-40</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I10" t="n">
+        <v>120</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-40</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-40</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" t="n">
+        <v>120</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-40</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-40</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>10</v>
+      </c>
+      <c r="I12" t="n">
+        <v>120</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-40</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-40</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="J6" t="n">
-        <v>-4</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-4</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" t="n">
+        <v>120</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-40</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-40</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" t="n">
+        <v>120</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-40</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-40</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>10</v>
+      </c>
+      <c r="I15" t="n">
+        <v>120</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-40</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-40</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-40</v>
       </c>
     </row>
   </sheetData>
@@ -1018,7 +1495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1064,7 +1541,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>阿狗(东风)</t>
+          <t>奶猫(东风)</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -1089,7 +1566,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1107,7 +1584,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1137,7 +1614,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1150,33 +1627,33 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>放炮</t>
+          <t>自摸</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>/</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>-4</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
       <c r="L3" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="4">
@@ -1185,7 +1662,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1198,33 +1675,33 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>放炮</t>
+          <t>自摸</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>/</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>-4</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
       <c r="L4" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="5">
@@ -1233,7 +1710,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1246,33 +1723,33 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>放炮</t>
+          <t>自摸</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>/</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>-4</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
       <c r="L5" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="6">
@@ -1281,7 +1758,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1294,273 +1771,33 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>放炮</t>
+          <t>自摸</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>/</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>-4</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
       <c r="L6" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>老王</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>6</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>老王</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>6</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>老王</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>老王</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>6</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>老王</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>6</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
   </sheetData>
@@ -1574,6 +1811,562 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>局号</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>庄家</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>连庄次数</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>庄倍数</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>本局结果</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>胡牌选手</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>放炮选手</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>番数</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>阿狗(东风)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>农少(南风)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>老王(西风)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>老野(北风)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/麻坛所有比赛数据.xlsx
+++ b/麻坛所有比赛数据.xlsx
@@ -705,7 +705,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -713,7 +713,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -721,7 +721,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>老潘</t>
+          <t>老王</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -747,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,17 +793,17 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>农少(东风)</t>
+          <t>老潘(东风)</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>老王(南风)</t>
+          <t>农少(南风)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>老潘(西风)</t>
+          <t>老王(西风)</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="J2" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="K2" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="L2" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="3">
@@ -866,7 +866,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -893,19 +893,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="K3" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="L3" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="4">
@@ -914,7 +914,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -941,19 +941,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="K4" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="L4" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="5">
@@ -962,7 +962,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -989,19 +989,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="K5" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="L5" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="6">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1037,19 +1037,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="K6" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="L6" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="7">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1085,19 +1085,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="J7" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="K7" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="L7" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="8">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="J8" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="K8" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="L8" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="9">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="J9" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="K9" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="L9" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="10">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1229,19 +1229,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="J10" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="K10" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="L10" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="11">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1277,19 +1277,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="J11" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="K11" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="L11" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="12">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1325,19 +1325,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="J12" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="K12" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="L12" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="13">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1373,115 +1373,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="J13" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="K13" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="L13" t="n">
-        <v>-40</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>农少</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>自摸</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>农少</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>10</v>
-      </c>
-      <c r="I14" t="n">
-        <v>120</v>
-      </c>
-      <c r="J14" t="n">
-        <v>-40</v>
-      </c>
-      <c r="K14" t="n">
-        <v>-40</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-40</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>农少</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>自摸</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>农少</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>10</v>
-      </c>
-      <c r="I15" t="n">
-        <v>120</v>
-      </c>
-      <c r="J15" t="n">
-        <v>-40</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-40</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
     </row>
   </sheetData>

--- a/麻坛所有比赛数据.xlsx
+++ b/麻坛所有比赛数据.xlsx
@@ -8,10 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="比赛汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="对局明细_20260623" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="对局明细_20260622" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="对局明细_20260620" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="对局明细_20260621" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="对局明细_20260621" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="对局明细_20260623" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="对局明细_20260622" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="对局明细_20260620" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,6 +733,50 @@
         </is>
       </c>
       <c r="J7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>比赛_20260621</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -747,7 +791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,17 +837,17 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>老潘(东风)</t>
+          <t>奶猫(东风)</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>农少(南风)</t>
+          <t>老王(南风)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>老王(西风)</t>
+          <t>阿狗(西风)</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
@@ -818,7 +862,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>老潘</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -836,7 +880,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>老潘</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -845,19 +889,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="J2" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
       <c r="K2" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
       <c r="L2" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="3">
@@ -866,7 +910,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>老潘</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -884,7 +928,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>老潘</t>
+          <t>老王</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -893,19 +937,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
-        <v>12</v>
+        <v>-40</v>
       </c>
       <c r="J3" t="n">
-        <v>-4</v>
+        <v>80</v>
       </c>
       <c r="K3" t="n">
-        <v>-4</v>
+        <v>-20</v>
       </c>
       <c r="L3" t="n">
-        <v>-4</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="4">
@@ -914,7 +958,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>老潘</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -932,7 +976,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>老潘</t>
+          <t>阿狗</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -941,19 +985,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>-40</v>
       </c>
       <c r="J4" t="n">
-        <v>-4</v>
+        <v>-20</v>
       </c>
       <c r="K4" t="n">
-        <v>-4</v>
+        <v>80</v>
       </c>
       <c r="L4" t="n">
-        <v>-4</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="5">
@@ -962,7 +1006,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>老潘</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -980,7 +1024,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>老潘</t>
+          <t>老野</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -989,19 +1033,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
+        <v>-40</v>
       </c>
       <c r="J5" t="n">
-        <v>-4</v>
+        <v>-20</v>
       </c>
       <c r="K5" t="n">
-        <v>-4</v>
+        <v>-20</v>
       </c>
       <c r="L5" t="n">
-        <v>-4</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6">
@@ -1010,7 +1054,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>老潘</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1028,7 +1072,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>老潘</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1037,19 +1081,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="J6" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
       <c r="K6" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
       <c r="L6" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="7">
@@ -1058,7 +1102,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>老潘</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1076,7 +1120,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>老潘</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1085,19 +1129,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="J7" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
       <c r="K7" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
       <c r="L7" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="8">
@@ -1106,7 +1150,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>老潘</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1124,7 +1168,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>老潘</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1133,19 +1177,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="J8" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
       <c r="K8" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
       <c r="L8" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="9">
@@ -1154,7 +1198,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>老潘</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1172,7 +1216,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>老潘</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1181,19 +1225,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I9" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="J9" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
       <c r="K9" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
       <c r="L9" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="10">
@@ -1202,7 +1246,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>老潘</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1220,7 +1264,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>老潘</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1229,19 +1273,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I10" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="J10" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
       <c r="K10" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
       <c r="L10" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="11">
@@ -1250,7 +1294,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>老潘</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1268,7 +1312,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>老潘</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1277,115 +1321,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="J11" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
       <c r="K11" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
       <c r="L11" t="n">
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>老潘</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>自摸</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>老潘</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" t="n">
-        <v>12</v>
-      </c>
-      <c r="J12" t="n">
-        <v>-4</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L12" t="n">
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>老潘</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>自摸</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>老潘</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>12</v>
-      </c>
-      <c r="J13" t="n">
-        <v>-4</v>
-      </c>
-      <c r="K13" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-4</v>
+        <v>-40</v>
       </c>
     </row>
   </sheetData>
@@ -1399,7 +1347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1445,7 +1393,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>奶猫(东风)</t>
+          <t>老潘(东风)</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -1470,7 +1418,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1488,7 +1436,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1518,7 +1466,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1536,7 +1484,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1566,7 +1514,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1584,7 +1532,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1614,7 +1562,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1632,7 +1580,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1662,7 +1610,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1680,7 +1628,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>老潘</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1701,6 +1649,342 @@
         <v>-4</v>
       </c>
       <c r="L6" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>老潘</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>老潘</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>老潘</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>老潘</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>12</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>老潘</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>老潘</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>12</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>老潘</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>老潘</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>12</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>老潘</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>老潘</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>12</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>老潘</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>老潘</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>老潘</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>老潘</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>12</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L13" t="n">
         <v>-4</v>
       </c>
     </row>
@@ -1715,7 +1999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1761,7 +2045,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>阿狗(东风)</t>
+          <t>奶猫(东风)</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -1786,7 +2070,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1804,7 +2088,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1834,7 +2118,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1847,33 +2131,33 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>放炮</t>
+          <t>自摸</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>/</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>-4</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
       <c r="L3" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="4">
@@ -1882,7 +2166,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1895,33 +2179,33 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>放炮</t>
+          <t>自摸</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>/</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>-4</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
       <c r="L4" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="5">
@@ -1930,7 +2214,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1943,33 +2227,33 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>放炮</t>
+          <t>自摸</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>/</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>-4</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
       <c r="L5" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="6">
@@ -1978,7 +2262,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1991,273 +2275,33 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>放炮</t>
+          <t>自摸</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>/</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>-4</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
       <c r="L6" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>老王</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>6</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>老王</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>6</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>老王</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>老王</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>6</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>老王</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>6</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
   </sheetData>
@@ -2271,7 +2315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2355,33 +2399,33 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>放炮</t>
+          <t>自摸</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>阿狗</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>/</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>-4</v>
+        <v>12</v>
       </c>
       <c r="J2" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>-4</v>
       </c>
       <c r="L2" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="3">
@@ -2813,438 +2857,6 @@
         <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>农少</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>农少</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>6</v>
-      </c>
-      <c r="K13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>农少</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J14" t="n">
-        <v>6</v>
-      </c>
-      <c r="K14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>农少</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J15" t="n">
-        <v>6</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>农少</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J16" t="n">
-        <v>6</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>农少</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>6</v>
-      </c>
-      <c r="K17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>农少</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>6</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>农少</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J19" t="n">
-        <v>6</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>放炮</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>农少</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>阿狗</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J20" t="n">
-        <v>6</v>
-      </c>
-      <c r="K20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L20" t="n">
         <v>-1</v>
       </c>
     </row>

--- a/麻坛所有比赛数据.xlsx
+++ b/麻坛所有比赛数据.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet name="比赛汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="对局明细_20260621" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="对局明细_20260624" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="对局明细_20260623" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="对局明细_20260622" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="对局明细_20260620" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="对局明细_20260621" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -739,12 +740,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>比赛_20260621</t>
+          <t>比赛_20260624</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -757,7 +758,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -765,7 +766,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>老王</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -842,12 +843,12 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>老王(南风)</t>
+          <t>农少(南风)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>阿狗(西风)</t>
+          <t>老王(西风)</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
@@ -889,19 +890,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="J2" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="K2" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="L2" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="3">
@@ -928,7 +929,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -937,19 +938,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>-40</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>80</v>
+        <v>-4</v>
       </c>
       <c r="K3" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
       <c r="L3" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="4">
@@ -976,7 +977,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>阿狗</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -985,19 +986,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>-40</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
       <c r="K4" t="n">
-        <v>80</v>
+        <v>-4</v>
       </c>
       <c r="L4" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="5">
@@ -1024,7 +1025,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>老野</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1033,19 +1034,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>-40</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
       <c r="K5" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
       <c r="L5" t="n">
-        <v>80</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="6">
@@ -1081,19 +1082,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="K6" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="L6" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="7">
@@ -1129,19 +1130,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="J7" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="K7" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="L7" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="8">
@@ -1177,19 +1178,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="J8" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="K8" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="L8" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="9">
@@ -1225,19 +1226,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="J9" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="K9" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="L9" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="10">
@@ -1273,19 +1274,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="J10" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="K10" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="L10" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="11">
@@ -1321,19 +1322,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>120</v>
+        <v>12</v>
       </c>
       <c r="J11" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="K11" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
       <c r="L11" t="n">
-        <v>-40</v>
+        <v>-4</v>
       </c>
     </row>
   </sheetData>
@@ -2863,4 +2864,992 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>局号</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>庄家</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>连庄次数</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>庄倍数</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>本局结果</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>胡牌选手</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>放炮选手</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>番数</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>阿狗(东风)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>农少(南风)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>老王(西风)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>老野(北风)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>6</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>6</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>6</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>6</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>阿狗</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/麻坛所有比赛数据.xlsx
+++ b/麻坛所有比赛数据.xlsx
@@ -1,80 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067A9368-04CE-41DC-8AB1-636DEC61B87E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="9230" yWindow="4130" windowWidth="18470" windowHeight="15460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="比赛汇总" sheetId="1" r:id="rId1"/>
+    <sheet name="比赛汇总" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="对局明细_20260621" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>比赛名称</t>
-  </si>
-  <si>
-    <t>比赛日期</t>
-  </si>
-  <si>
-    <t>第1名</t>
-  </si>
-  <si>
-    <t>第1名名次分</t>
-  </si>
-  <si>
-    <t>第2名</t>
-  </si>
-  <si>
-    <t>第2名名次分</t>
-  </si>
-  <si>
-    <t>第3名</t>
-  </si>
-  <si>
-    <t>第3名名次分</t>
-  </si>
-  <si>
-    <t>第4名</t>
-  </si>
-  <si>
-    <t>第4名名次分</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -93,21 +48,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -395,44 +409,427 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>比赛名称</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>比赛日期</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>第1名</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>第1名名次分</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>第2名</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>第2名名次分</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>第3名</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>第3名名次分</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>第4名</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>第4名名次分</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>比赛_20260621</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>局号</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>庄家</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>连庄次数</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>庄倍数</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>本局结果</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>胡牌选手</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>放炮选手</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>番数</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>奶猫(东风)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>农少(南风)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>老王(西风)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>老野(北风)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>12</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>12</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>12</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/麻坛所有比赛数据.xlsx
+++ b/麻坛所有比赛数据.xlsx
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>比赛_20260621</t>
+          <t>比赛_20260622</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -490,7 +490,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -625,10 +625,10 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J2" t="n">
         <v>12</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-4</v>
       </c>
       <c r="K2" t="n">
         <v>-4</v>
@@ -643,7 +643,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -673,10 +673,10 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J3" t="n">
         <v>12</v>
-      </c>
-      <c r="J3" t="n">
-        <v>-4</v>
       </c>
       <c r="K3" t="n">
         <v>-4</v>
@@ -691,7 +691,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J4" t="n">
         <v>12</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-4</v>
       </c>
       <c r="K4" t="n">
         <v>-4</v>
@@ -739,7 +739,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -769,10 +769,10 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J5" t="n">
         <v>12</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-4</v>
       </c>
       <c r="K5" t="n">
         <v>-4</v>
@@ -787,7 +787,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -817,10 +817,10 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J6" t="n">
         <v>12</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-4</v>
       </c>
       <c r="K6" t="n">
         <v>-4</v>

--- a/麻坛所有比赛数据.xlsx
+++ b/麻坛所有比赛数据.xlsx
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>比赛_20260622</t>
+          <t>比赛_20260623</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,7 +482,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老野</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -506,7 +506,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>老野</t>
+          <t>老王</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老野</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老野</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -628,13 +628,13 @@
         <v>-4</v>
       </c>
       <c r="J2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L2" t="n">
         <v>12</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-4</v>
       </c>
     </row>
     <row r="3">
@@ -643,7 +643,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老野</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老野</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -676,13 +676,13 @@
         <v>-4</v>
       </c>
       <c r="J3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L3" t="n">
         <v>12</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-4</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老野</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老野</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -724,13 +724,13 @@
         <v>-4</v>
       </c>
       <c r="J4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L4" t="n">
         <v>12</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-4</v>
       </c>
     </row>
     <row r="5">
@@ -739,7 +739,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老野</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老野</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -772,13 +772,13 @@
         <v>-4</v>
       </c>
       <c r="J5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L5" t="n">
         <v>12</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-4</v>
       </c>
     </row>
     <row r="6">
@@ -787,7 +787,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老野</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老野</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -820,13 +820,205 @@
         <v>-4</v>
       </c>
       <c r="J6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L6" t="n">
         <v>12</v>
       </c>
-      <c r="K6" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-4</v>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/麻坛所有比赛数据.xlsx
+++ b/麻坛所有比赛数据.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="比赛汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="对局明细_20260621" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="对局明细_20260609" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,17 +472,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>比赛_20260623</t>
+          <t>比赛_20260609</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>老野</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -490,7 +490,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>老王</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -506,7 +506,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>老野</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>老野</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>老野</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -625,7 +625,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>-4</v>
+        <v>12</v>
       </c>
       <c r="J2" t="n">
         <v>-4</v>
@@ -634,7 +634,7 @@
         <v>-4</v>
       </c>
       <c r="L2" t="n">
-        <v>12</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="3">
@@ -643,7 +643,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>老野</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>老野</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -673,7 +673,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>-4</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
         <v>-4</v>
@@ -682,7 +682,7 @@
         <v>-4</v>
       </c>
       <c r="L3" t="n">
-        <v>12</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>老野</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>老野</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -721,7 +721,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>-4</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
         <v>-4</v>
@@ -730,7 +730,7 @@
         <v>-4</v>
       </c>
       <c r="L4" t="n">
-        <v>12</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="5">
@@ -739,7 +739,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>老野</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>老野</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -769,7 +769,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>-4</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
         <v>-4</v>
@@ -778,7 +778,7 @@
         <v>-4</v>
       </c>
       <c r="L5" t="n">
-        <v>12</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="6">
@@ -787,7 +787,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>老野</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>老野</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -817,7 +817,7 @@
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>-4</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
         <v>-4</v>
@@ -826,7 +826,7 @@
         <v>-4</v>
       </c>
       <c r="L6" t="n">
-        <v>12</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="7">
@@ -835,7 +835,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>老野</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>老野</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -865,7 +865,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>-4</v>
+        <v>12</v>
       </c>
       <c r="J7" t="n">
         <v>-4</v>
@@ -874,7 +874,7 @@
         <v>-4</v>
       </c>
       <c r="L7" t="n">
-        <v>12</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="8">
@@ -883,7 +883,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>老野</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>老野</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -913,7 +913,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>-4</v>
+        <v>12</v>
       </c>
       <c r="J8" t="n">
         <v>-4</v>
@@ -922,103 +922,7 @@
         <v>-4</v>
       </c>
       <c r="L8" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>老野</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>自摸</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>老野</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>-4</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L9" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>老野</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>第一庄（2倍）</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>自摸</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>老野</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-4</v>
-      </c>
-      <c r="K10" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L10" t="n">
-        <v>12</v>
+        <v>-4</v>
       </c>
     </row>
   </sheetData>

--- a/麻坛所有比赛数据.xlsx
+++ b/麻坛所有比赛数据.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="比赛汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="对局明细_20260609" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="明细_20260621_比赛_20260621" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="对局明细_20260609" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,6 +511,50 @@
         </is>
       </c>
       <c r="J2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>比赛_20260621</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -524,6 +569,1906 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>局号</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>庄家</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>连庄次数</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>庄倍数</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>本局结果</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>胡牌选手</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>放炮选手</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>番数</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>奶猫(东风)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>农少(南风)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>老王(西风)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>老野(北风)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I2" t="n">
+        <v>120</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-40</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-40</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I3" t="n">
+        <v>120</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-40</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-40</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-40</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L4" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-40</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L5" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L6" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J7" t="n">
+        <v>50</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J8" t="n">
+        <v>50</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J9" t="n">
+        <v>50</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-40</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-20</v>
+      </c>
+      <c r="K10" t="n">
+        <v>80</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-40</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-20</v>
+      </c>
+      <c r="K11" t="n">
+        <v>80</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>10</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-40</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-20</v>
+      </c>
+      <c r="K12" t="n">
+        <v>80</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-40</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-20</v>
+      </c>
+      <c r="K13" t="n">
+        <v>80</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" t="n">
+        <v>50</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-20</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>10</v>
+      </c>
+      <c r="I15" t="n">
+        <v>50</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-20</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>10</v>
+      </c>
+      <c r="I16" t="n">
+        <v>50</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-20</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>10</v>
+      </c>
+      <c r="I17" t="n">
+        <v>50</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-20</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>10</v>
+      </c>
+      <c r="I18" t="n">
+        <v>50</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-20</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>10</v>
+      </c>
+      <c r="I19" t="n">
+        <v>60</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-40</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>10</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J20" t="n">
+        <v>50</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>10</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J21" t="n">
+        <v>50</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>10</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J22" t="n">
+        <v>50</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>10</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J23" t="n">
+        <v>50</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>10</v>
+      </c>
+      <c r="I24" t="n">
+        <v>50</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-20</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>10</v>
+      </c>
+      <c r="I25" t="n">
+        <v>50</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-20</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>10</v>
+      </c>
+      <c r="I26" t="n">
+        <v>50</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-20</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>10</v>
+      </c>
+      <c r="I27" t="n">
+        <v>50</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-20</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>10</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L28" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>10</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L29" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>10</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L30" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>10</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L31" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>10</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-10</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L32" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>10</v>
+      </c>
+      <c r="I33" t="n">
+        <v>50</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-20</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>10</v>
+      </c>
+      <c r="I34" t="n">
+        <v>50</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-20</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>10</v>
+      </c>
+      <c r="I35" t="n">
+        <v>50</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-20</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>10</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J36" t="n">
+        <v>50</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>10</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J37" t="n">
+        <v>50</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>10</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J38" t="n">
+        <v>50</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>10</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J39" t="n">
+        <v>50</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/麻坛所有比赛数据.xlsx
+++ b/麻坛所有比赛数据.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="比赛汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="明细_20260622_比赛_20260622" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="对局明细_20260609" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="明细_20260625_比赛_20260625" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="明细_20260622_比赛_20260622" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="对局明细_20260609" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,6 +556,50 @@
         </is>
       </c>
       <c r="J3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>比赛_20260625</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>老潘</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -569,7 +614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -615,17 +660,17 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>奶猫(东风)</t>
+          <t>农少(东风)</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>农少(南风)</t>
+          <t>老王(南风)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>老王(西风)</t>
+          <t>老潘(西风)</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
@@ -640,7 +685,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -653,7 +698,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>放炮</t>
+          <t>自摸</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -663,23 +708,23 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>/</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>-20</v>
+        <v>12</v>
       </c>
       <c r="J2" t="n">
-        <v>50</v>
+        <v>-4</v>
       </c>
       <c r="K2" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
       <c r="L2" t="n">
-        <v>-10</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="3">
@@ -688,7 +733,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -701,7 +746,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>放炮</t>
+          <t>自摸</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -711,23 +756,23 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>/</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>-20</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>50</v>
+        <v>-4</v>
       </c>
       <c r="K3" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
       <c r="L3" t="n">
-        <v>-10</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="4">
@@ -736,7 +781,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -749,7 +794,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>放炮</t>
+          <t>自摸</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -759,23 +804,23 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>/</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>-20</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>50</v>
+        <v>-4</v>
       </c>
       <c r="K4" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
       <c r="L4" t="n">
-        <v>-10</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="5">
@@ -784,7 +829,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -797,7 +842,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>放炮</t>
+          <t>自摸</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -807,23 +852,23 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>/</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>-20</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>50</v>
+        <v>-4</v>
       </c>
       <c r="K5" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
       <c r="L5" t="n">
-        <v>-10</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="6">
@@ -832,7 +877,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -845,7 +890,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>放炮</t>
+          <t>自摸</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -855,23 +900,23 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>/</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>-20</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>50</v>
+        <v>-4</v>
       </c>
       <c r="K6" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
       <c r="L6" t="n">
-        <v>-10</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="7">
@@ -880,7 +925,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -893,7 +938,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>放炮</t>
+          <t>自摸</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -903,23 +948,23 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>/</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>-20</v>
+        <v>12</v>
       </c>
       <c r="J7" t="n">
-        <v>50</v>
+        <v>-4</v>
       </c>
       <c r="K7" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
       <c r="L7" t="n">
-        <v>-10</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="8">
@@ -928,7 +973,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -941,7 +986,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>放炮</t>
+          <t>自摸</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -951,23 +996,23 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>/</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>-20</v>
+        <v>12</v>
       </c>
       <c r="J8" t="n">
-        <v>50</v>
+        <v>-4</v>
       </c>
       <c r="K8" t="n">
-        <v>-20</v>
+        <v>-4</v>
       </c>
       <c r="L8" t="n">
-        <v>-10</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="9">
@@ -976,7 +1021,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -989,7 +1034,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>放炮</t>
+          <t>自摸</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -999,23 +1044,215 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>奶猫</t>
+          <t>/</t>
         </is>
       </c>
       <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>12</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>12</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="I9" t="n">
-        <v>-20</v>
-      </c>
-      <c r="J9" t="n">
-        <v>50</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-20</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-10</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>12</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>12</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-4</v>
       </c>
     </row>
   </sheetData>
@@ -1029,6 +1266,466 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>局号</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>庄家</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>连庄次数</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>庄倍数</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>本局结果</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>胡牌选手</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>放炮选手</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>番数</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>奶猫(东风)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>农少(南风)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>老王(西风)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>老野(北风)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J3" t="n">
+        <v>50</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J4" t="n">
+        <v>50</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J5" t="n">
+        <v>50</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J6" t="n">
+        <v>50</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J7" t="n">
+        <v>50</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J8" t="n">
+        <v>50</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>放炮</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J9" t="n">
+        <v>50</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/麻坛所有比赛数据.xlsx
+++ b/麻坛所有比赛数据.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="比赛汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="明细_20260625_比赛_20260625" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="明细_20260627_比赛_20260627" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="明细_20260622_比赛_20260622" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="对局明细_20260609" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
@@ -562,17 +562,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>比赛_20260625</t>
+          <t>比赛_20260627</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -580,7 +580,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>老王</t>
+          <t>老野</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -588,7 +588,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>老潘</t>
+          <t>老王</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>老野</t>
+          <t>农少</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -614,7 +614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -660,17 +660,17 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>农少(东风)</t>
+          <t>奶猫(东风)</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>老王(南风)</t>
+          <t>农少(南风)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>老潘(西风)</t>
+          <t>老王(西风)</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>农少</t>
+          <t>奶猫</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1253,6 +1253,1686 @@
       </c>
       <c r="L13" t="n">
         <v>-4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>12</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>8</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>8</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>8</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>奶猫</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>8</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>8</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K28" t="n">
+        <v>8</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K29" t="n">
+        <v>8</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K30" t="n">
+        <v>8</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K31" t="n">
+        <v>8</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K32" t="n">
+        <v>8</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K33" t="n">
+        <v>8</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>老王</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K34" t="n">
+        <v>8</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L35" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L36" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L37" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L38" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J39" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L39" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J40" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K40" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L40" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J41" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L41" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L42" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>第一庄（2倍）</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J43" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L43" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>第三庄及以上（8倍）</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>8</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J44" t="n">
+        <v>-16</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L44" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>第三庄及以上（8倍）</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>8</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J45" t="n">
+        <v>-16</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L45" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>第三庄及以上（8倍）</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>8</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J46" t="n">
+        <v>-16</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L46" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>第三庄及以上（8倍）</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>8</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J47" t="n">
+        <v>-16</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L47" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>农少</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>第三庄及以上（8倍）</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>8</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>自摸</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>老野</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J48" t="n">
+        <v>-16</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L48" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
